--- a/data/trans_orig/P19C02-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P19C02-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue una limpieza de boca en 2007</t>
+          <t>Población según si el motivo por su última visita al dentista fue una limpieza de boca en 2007 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>98165</t>
+          <t>97033</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>137693</t>
+          <t>136073</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>136556</t>
+          <t>138433</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>181489</t>
+          <t>181743</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>247988</t>
+          <t>249501</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>310072</t>
+          <t>310533</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,84%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>551672</t>
+          <t>553292</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>591200</t>
+          <t>592332</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>777470</t>
+          <t>777216</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>822403</t>
+          <t>820526</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1338252</t>
+          <t>1337791</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1400336</t>
+          <t>1398823</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,86%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>373156</t>
+          <t>369852</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>440638</t>
+          <t>438359</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>427122</t>
+          <t>429229</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>502573</t>
+          <t>497258</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>816291</t>
+          <t>815719</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>916310</t>
+          <t>912707</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,0%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>873810</t>
+          <t>876089</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>941292</t>
+          <t>944596</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>867694</t>
+          <t>873009</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>943145</t>
+          <t>941038</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1768405</t>
+          <t>1772008</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1868424</t>
+          <t>1868996</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,62%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>156815</t>
+          <t>159463</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>202162</t>
+          <t>201307</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>153233</t>
+          <t>154627</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>195568</t>
+          <t>196088</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>329720</t>
+          <t>326015</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>390539</t>
+          <t>386364</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>44,94%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>248767</t>
+          <t>249622</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>294114</t>
+          <t>291466</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>213215</t>
+          <t>212695</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>255550</t>
+          <t>254156</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>469173</t>
+          <t>473348</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>529992</t>
+          <t>533697</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>62,08%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>660275</t>
+          <t>658676</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>751819</t>
+          <t>746373</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>754103</t>
+          <t>747514</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>843476</t>
+          <t>844575</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1431757</t>
+          <t>1434830</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1566168</t>
+          <t>1562899</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,1%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1702923</t>
+          <t>1708369</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1794467</t>
+          <t>1796066</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1894533</t>
+          <t>1893434</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1983906</t>
+          <t>1990495</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3626582</t>
+          <t>3629851</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3760993</t>
+          <t>3757920</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,37%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue una limpieza de boca en 2012</t>
+          <t>Población según si el motivo por su última visita al dentista fue una limpieza de boca en 2012 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>99100</t>
+          <t>99075</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>139501</t>
+          <t>141043</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>209989</t>
+          <t>208616</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>268831</t>
+          <t>264485</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>318629</t>
+          <t>321829</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>389963</t>
+          <t>391387</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,53%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>637612</t>
+          <t>636070</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>678013</t>
+          <t>678038</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>860453</t>
+          <t>864799</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>919295</t>
+          <t>920668</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1516434</t>
+          <t>1515010</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1587768</t>
+          <t>1584568</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,12%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>522241</t>
+          <t>521085</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>601277</t>
+          <t>602563</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>530536</t>
+          <t>529194</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>606476</t>
+          <t>610176</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1070468</t>
+          <t>1070157</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1188917</t>
+          <t>1180449</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,01%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1086009</t>
+          <t>1084723</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1165045</t>
+          <t>1166201</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>984740</t>
+          <t>981040</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1060680</t>
+          <t>1062022</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2089585</t>
+          <t>2098053</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2208034</t>
+          <t>2208345</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,36%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>160370</t>
+          <t>161332</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>204567</t>
+          <t>204734</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>155593</t>
+          <t>154359</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>197851</t>
+          <t>196539</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>330095</t>
+          <t>329993</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>391157</t>
+          <t>392512</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>45,33%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>237567</t>
+          <t>237400</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>281764</t>
+          <t>280802</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>225872</t>
+          <t>227184</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>268130</t>
+          <t>269364</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>474700</t>
+          <t>473345</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>535762</t>
+          <t>535864</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>61,89%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>811790</t>
+          <t>811352</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>908276</t>
+          <t>914662</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>930761</t>
+          <t>920435</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1042037</t>
+          <t>1029653</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1759854</t>
+          <t>1775601</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1914031</t>
+          <t>1914304</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,64%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1998257</t>
+          <t>1991871</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2094743</t>
+          <t>2095181</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2102186</t>
+          <t>2114570</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2213462</t>
+          <t>2223788</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4136725</t>
+          <t>4136452</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4290902</t>
+          <t>4275155</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>70,65%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue una limpieza de boca en 2016</t>
+          <t>Población según si el motivo por su última visita al dentista fue una limpieza de boca en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>78124</t>
+          <t>77125</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>112003</t>
+          <t>111225</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>140353</t>
+          <t>138464</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>184585</t>
+          <t>183978</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>227569</t>
+          <t>226271</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>283510</t>
+          <t>281253</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,65%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>345416</t>
+          <t>346194</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>379295</t>
+          <t>380294</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>454289</t>
+          <t>454896</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>498521</t>
+          <t>500410</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>812783</t>
+          <t>815040</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>868724</t>
+          <t>870022</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>79,36%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>555450</t>
+          <t>554629</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>635721</t>
+          <t>635654</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>633086</t>
+          <t>634275</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>710615</t>
+          <t>718466</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1215847</t>
+          <t>1209347</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1328719</t>
+          <t>1325466</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>38,92%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1060884</t>
+          <t>1060951</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1141155</t>
+          <t>1141976</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>998104</t>
+          <t>990253</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1075633</t>
+          <t>1074444</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2076605</t>
+          <t>2079858</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2189477</t>
+          <t>2195977</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>64,49%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>213270</t>
+          <t>215201</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>259732</t>
+          <t>261108</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>52,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>205524</t>
+          <t>209543</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>252477</t>
+          <t>254480</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>434168</t>
+          <t>436806</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>498614</t>
+          <t>501634</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>49,79%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>239512</t>
+          <t>238136</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>285974</t>
+          <t>284043</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>255843</t>
+          <t>253840</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>302796</t>
+          <t>298777</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>508950</t>
+          <t>505930</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>573396</t>
+          <t>570758</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>56,65%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>879364</t>
+          <t>874958</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>977640</t>
+          <t>979125</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1009785</t>
+          <t>1012957</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1119729</t>
+          <t>1118197</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1917621</t>
+          <t>1919151</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2066975</t>
+          <t>2065912</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,5%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1675629</t>
+          <t>1674144</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1773905</t>
+          <t>1778311</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1736184</t>
+          <t>1737716</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1846128</t>
+          <t>1842956</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3442207</t>
+          <t>3443270</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3591561</t>
+          <t>3590031</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>65,16%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue una limpieza de boca en 2023</t>
+          <t>Población según si el motivo por su última visita al dentista fue una limpieza de boca en 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>92140</t>
+          <t>92359</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>127037</t>
+          <t>128709</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>213194</t>
+          <t>212509</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>250715</t>
+          <t>250826</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>315701</t>
+          <t>313254</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>365735</t>
+          <t>366057</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,35%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>357404</t>
+          <t>355732</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>392301</t>
+          <t>392082</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>470901</t>
+          <t>470790</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>508422</t>
+          <t>509107</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>840322</t>
+          <t>840000</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>890356</t>
+          <t>892803</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>74,03%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>634849</t>
+          <t>705177</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1109848</t>
+          <t>1112896</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1029565</t>
+          <t>1034319</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1429156</t>
+          <t>1448317</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1820743</t>
+          <t>1821162</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2469743</t>
+          <t>2426135</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>54,8%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1119723</t>
+          <t>1116675</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1594722</t>
+          <t>1524394</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>768750</t>
+          <t>749589</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1168341</t>
+          <t>1163587</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1957734</t>
+          <t>2001342</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2606734</t>
+          <t>2606315</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>58,87%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>349782</t>
+          <t>349909</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>400383</t>
+          <t>401637</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>349334</t>
+          <t>349115</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>393393</t>
+          <t>391624</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>706725</t>
+          <t>707751</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>777782</t>
+          <t>780283</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,79%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>231637</t>
+          <t>230383</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>282238</t>
+          <t>282111</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>258218</t>
+          <t>259987</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>302277</t>
+          <t>302496</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>505850</t>
+          <t>503349</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>576907</t>
+          <t>575881</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>44,86%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1134340</t>
+          <t>1089132</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1596700</t>
+          <t>1588626</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1633899</t>
+          <t>1644252</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2092172</t>
+          <t>2144563</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2892540</t>
+          <t>2897182</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3517341</t>
+          <t>3531425</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>51,05%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1749332</t>
+          <t>1757406</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2211692</t>
+          <t>2256900</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1478961</t>
+          <t>1426570</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1937234</t>
+          <t>1926881</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3399824</t>
+          <t>3385740</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4024625</t>
+          <t>4019983</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>58,12%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19C02-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P19C02-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>97033</t>
+          <t>97770</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>136073</t>
+          <t>137517</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>138433</t>
+          <t>137320</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>181743</t>
+          <t>185001</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>249501</t>
+          <t>245956</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>310533</t>
+          <t>309228</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,76%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>553292</t>
+          <t>551848</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>592332</t>
+          <t>591595</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>777216</t>
+          <t>773958</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>820526</t>
+          <t>821639</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1337791</t>
+          <t>1339096</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1398823</t>
+          <t>1402368</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>85,08%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>369852</t>
+          <t>371325</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>438359</t>
+          <t>439067</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>429229</t>
+          <t>426405</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>497258</t>
+          <t>496667</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>815719</t>
+          <t>818145</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>912707</t>
+          <t>918871</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>34,23%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>876089</t>
+          <t>875381</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>944596</t>
+          <t>943123</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>873009</t>
+          <t>873600</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>941038</t>
+          <t>943862</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1772008</t>
+          <t>1765844</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1868996</t>
+          <t>1866570</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>69,53%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>159463</t>
+          <t>156019</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>201307</t>
+          <t>200724</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>154627</t>
+          <t>156984</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>196088</t>
+          <t>196087</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>326015</t>
+          <t>327791</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>386364</t>
+          <t>386761</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>44,99%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>249622</t>
+          <t>250205</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>291466</t>
+          <t>294910</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>212695</t>
+          <t>212696</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>254156</t>
+          <t>251799</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>473348</t>
+          <t>472951</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>533697</t>
+          <t>531921</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>61,87%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>658676</t>
+          <t>659841</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>746373</t>
+          <t>748681</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>747514</t>
+          <t>752463</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>844575</t>
+          <t>845461</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1434830</t>
+          <t>1433902</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1562899</t>
+          <t>1560556</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,05%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1708369</t>
+          <t>1706061</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1796066</t>
+          <t>1794901</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1893434</t>
+          <t>1892548</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1990495</t>
+          <t>1985546</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3629851</t>
+          <t>3632194</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3757920</t>
+          <t>3758848</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,39%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>99075</t>
+          <t>98787</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>141043</t>
+          <t>138593</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>208616</t>
+          <t>210653</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>264485</t>
+          <t>266314</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>321829</t>
+          <t>319014</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>391387</t>
+          <t>393787</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,66%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>636070</t>
+          <t>638520</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>678038</t>
+          <t>678326</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>864799</t>
+          <t>862970</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>920668</t>
+          <t>918631</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1515010</t>
+          <t>1512610</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1584568</t>
+          <t>1587383</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,27%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>521085</t>
+          <t>524774</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>602563</t>
+          <t>602843</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>529194</t>
+          <t>530705</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>610176</t>
+          <t>609489</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1070157</t>
+          <t>1077169</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1180449</t>
+          <t>1187254</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>36,21%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1084723</t>
+          <t>1084443</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1166201</t>
+          <t>1162512</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>64,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>981040</t>
+          <t>981727</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1062022</t>
+          <t>1060511</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2098053</t>
+          <t>2091248</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2208345</t>
+          <t>2201333</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>67,14%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>161332</t>
+          <t>157581</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>204734</t>
+          <t>203680</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>154359</t>
+          <t>156895</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>196539</t>
+          <t>198565</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>329993</t>
+          <t>327980</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>392512</t>
+          <t>390821</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>45,14%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>237400</t>
+          <t>238454</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>280802</t>
+          <t>284553</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>227184</t>
+          <t>225158</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>269364</t>
+          <t>266828</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>473345</t>
+          <t>475036</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>535864</t>
+          <t>537877</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>62,12%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>811352</t>
+          <t>806970</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>914662</t>
+          <t>914119</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>920435</t>
+          <t>922637</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1029653</t>
+          <t>1034041</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1775601</t>
+          <t>1766577</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1914304</t>
+          <t>1919501</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,72%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1991871</t>
+          <t>1992414</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2095181</t>
+          <t>2099563</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2114570</t>
+          <t>2110182</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2223788</t>
+          <t>2221586</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4136452</t>
+          <t>4131255</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4275155</t>
+          <t>4284179</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>70,8%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>77125</t>
+          <t>75925</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>111225</t>
+          <t>110182</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>138464</t>
+          <t>139311</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>183978</t>
+          <t>184517</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>226271</t>
+          <t>228134</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>281253</t>
+          <t>285056</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>26,0%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>346194</t>
+          <t>347237</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>380294</t>
+          <t>381494</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>454896</t>
+          <t>454357</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>500410</t>
+          <t>499563</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>815040</t>
+          <t>811237</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>870022</t>
+          <t>868159</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,19%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>554629</t>
+          <t>552452</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>635654</t>
+          <t>637314</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>634275</t>
+          <t>633738</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>718466</t>
+          <t>714479</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1209347</t>
+          <t>1217702</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1325466</t>
+          <t>1328124</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>39,0%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1060951</t>
+          <t>1059291</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1141976</t>
+          <t>1144153</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>990253</t>
+          <t>994240</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1074444</t>
+          <t>1074981</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2079858</t>
+          <t>2077200</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2195977</t>
+          <t>2187622</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>64,24%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>215201</t>
+          <t>214876</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>261108</t>
+          <t>262186</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>209543</t>
+          <t>208411</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>254480</t>
+          <t>253199</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>436806</t>
+          <t>434897</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>501634</t>
+          <t>500882</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>49,71%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>238136</t>
+          <t>237058</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>284043</t>
+          <t>284368</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>253840</t>
+          <t>255121</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>298777</t>
+          <t>299909</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>59,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>505930</t>
+          <t>506682</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>570758</t>
+          <t>572667</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>56,84%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>874958</t>
+          <t>874879</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>979125</t>
+          <t>976996</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1012957</t>
+          <t>1006284</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1118197</t>
+          <t>1117082</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1919151</t>
+          <t>1923707</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2065912</t>
+          <t>2068082</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,54%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1674144</t>
+          <t>1676273</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1778311</t>
+          <t>1778390</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1737716</t>
+          <t>1738831</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1842956</t>
+          <t>1849629</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3443270</t>
+          <t>3441100</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3590031</t>
+          <t>3585475</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>65,08%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>108659</t>
+          <t>123220</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>92359</t>
+          <t>105327</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>128709</t>
+          <t>143527</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>231220</t>
+          <t>258560</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>212509</t>
+          <t>238336</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>250826</t>
+          <t>278497</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>339879</t>
+          <t>381780</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>313254</t>
+          <t>352136</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>366057</t>
+          <t>410948</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>31,09%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>375782</t>
+          <t>414059</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>355732</t>
+          <t>393752</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>392082</t>
+          <t>431952</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>490396</t>
+          <t>526032</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>470790</t>
+          <t>506095</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>509107</t>
+          <t>546256</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>67,05%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>69,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>866178</t>
+          <t>940091</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>840000</t>
+          <t>910923</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>892803</t>
+          <t>969735</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>73,36%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>484441</t>
+          <t>537279</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>484441</t>
+          <t>537279</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>484441</t>
+          <t>537279</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>721616</t>
+          <t>784592</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>721616</t>
+          <t>784592</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>721616</t>
+          <t>784592</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1206057</t>
+          <t>1321871</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1206057</t>
+          <t>1321871</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1206057</t>
+          <t>1321871</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>971618</t>
+          <t>1053711</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>705177</t>
+          <t>1002788</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1112896</t>
+          <t>1108275</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1176096</t>
+          <t>1090849</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1034319</t>
+          <t>1043534</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1448317</t>
+          <t>1132296</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2147715</t>
+          <t>2144560</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1821162</t>
+          <t>2075293</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2426135</t>
+          <t>2210112</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>50,39%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>51,93%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1257953</t>
+          <t>1091845</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1116675</t>
+          <t>1037281</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1524394</t>
+          <t>1142768</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1021810</t>
+          <t>1019743</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>749589</t>
+          <t>978296</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1163587</t>
+          <t>1067058</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2279762</t>
+          <t>2111588</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2001342</t>
+          <t>2046036</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2606315</t>
+          <t>2180855</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>51,24%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2229571</t>
+          <t>2145556</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2229571</t>
+          <t>2145556</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2229571</t>
+          <t>2145556</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2197906</t>
+          <t>2110592</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2197906</t>
+          <t>2110592</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2197906</t>
+          <t>2110592</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4427477</t>
+          <t>4256148</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4427477</t>
+          <t>4256148</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4427477</t>
+          <t>4256148</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>375278</t>
+          <t>418958</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>349909</t>
+          <t>389814</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>401637</t>
+          <t>447015</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,22 +6258,22 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>370874</t>
+          <t>412196</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>349115</t>
+          <t>388149</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>391624</t>
+          <t>435856</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>746153</t>
+          <t>831153</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>707751</t>
+          <t>791943</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>780283</t>
+          <t>870300</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>60,98%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>256742</t>
+          <t>283835</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>230383</t>
+          <t>255778</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>282111</t>
+          <t>312979</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,27 +6371,27 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>280737</t>
+          <t>312217</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>259987</t>
+          <t>288557</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>302496</t>
+          <t>336264</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>537479</t>
+          <t>596053</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>503349</t>
+          <t>556906</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>575881</t>
+          <t>635263</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>44,51%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>632020</t>
+          <t>702793</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>632020</t>
+          <t>702793</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>632020</t>
+          <t>702793</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>651611</t>
+          <t>724413</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>651611</t>
+          <t>724413</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>651611</t>
+          <t>724413</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1283632</t>
+          <t>1427206</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1283632</t>
+          <t>1427206</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1283632</t>
+          <t>1427206</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1455556</t>
+          <t>1595888</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1089132</t>
+          <t>1532267</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1588626</t>
+          <t>1668282</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1778190</t>
+          <t>1761604</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1644252</t>
+          <t>1702361</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2144563</t>
+          <t>1813225</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>3233746</t>
+          <t>3357493</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2897182</t>
+          <t>3273316</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3531425</t>
+          <t>3446709</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>49,2%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1890476</t>
+          <t>1789740</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1757406</t>
+          <t>1717346</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2256900</t>
+          <t>1853361</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1792943</t>
+          <t>1857993</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1426570</t>
+          <t>1806372</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1926881</t>
+          <t>1917236</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>52,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3683419</t>
+          <t>3647732</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3385740</t>
+          <t>3558516</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4019983</t>
+          <t>3731909</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>53,27%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3346032</t>
+          <t>3385628</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3346032</t>
+          <t>3385628</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3346032</t>
+          <t>3385628</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3571133</t>
+          <t>3619597</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3571133</t>
+          <t>3619597</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3571133</t>
+          <t>3619597</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>6917165</t>
+          <t>7005225</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6917165</t>
+          <t>7005225</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6917165</t>
+          <t>7005225</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
